--- a/Health Check Scoring Dimension.xlsx
+++ b/Health Check Scoring Dimension.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9c6cd885c3c8140/Freelance Portugal 2026/Power BI Health Check tool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-krb\Claude Code Projects\Power BI Health Assessment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{9B509B3C-CE9C-4E4B-8221-CB6094980136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFF630CF-32AC-4918-B16B-E9A3008B4FAB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5A3C83-354D-4FA4-9A83-91AB37AFECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BDD7ADA1-7902-43EF-92B2-1A417B3FF5D8}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{BDD7ADA1-7902-43EF-92B2-1A417B3FF5D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2514" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3518" uniqueCount="1118">
   <si>
     <t>Question</t>
   </si>
@@ -2410,13 +2410,1015 @@
   </si>
   <si>
     <t>Maturity drives roadmap decisions</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Fix</t>
+  </si>
+  <si>
+    <t>Affected Users</t>
+  </si>
+  <si>
+    <t>Detailed Risk Explanation</t>
+  </si>
+  <si>
+    <t>Current state functional but limits optimization</t>
+  </si>
+  <si>
+    <t>Establish formal objectives framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Entire organization (20+ people)</t>
+  </si>
+  <si>
+    <t>Without documented Power BI objectives in your CoE strategy: 1) Reports built reactively in 'My Workspace' instead of governed workspaces - check Admin Portal &gt; Usage metrics showing 40% of content in personal workspaces. 2) Can't justify Premium capacity costs to finance - no documented success metrics to show in Power BI App usage reports. 3) Power BI Admin can't prioritize tenant setting changes without clear objectives. 4) Deployment pipeline strategy undefined. 5) Can't measure adoption via Admin Portal &gt; Usage metrics. Reference: Power BI Adoption Framework.</t>
+  </si>
+  <si>
+    <t>Critical absence creates operational chaos with uncontrolled processes and compliance exposure</t>
+  </si>
+  <si>
+    <t>Develop objectives guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Multiple departments (12-20 people)</t>
+  </si>
+  <si>
+    <t>Undocumented Power BI objectives: 1) Admins make tenant setting decisions inconsistently. 2) Premium capacity sizing guesswork - P1 (8.5 vCores) vs P2 (17 vCores) unclear. 3) Workspace licensing inconsistent (Pro vs PPU vs Premium). 4) External sharing policy unclear. 5) Gateway strategy undefined. Reference: Power BI licensing decision tree.</t>
+  </si>
+  <si>
+    <t>Partial implementation creates gaps and inconsistent outcomes</t>
+  </si>
+  <si>
+    <t>Standardize objectives approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>BI team + stakeholders (8-12 people)</t>
+  </si>
+  <si>
+    <t>Fragmented objectives: 1) Can't share datasets across licensing boundaries ('upgrade to Premium' errors). 2) Different RLS approaches by department. 3) Inconsistent ALM (deployment pipelines vs XMLA vs manual). 4) Dataflow usage inconsistent. 5) Sensitivity label application varies. Reference: Enterprise governance.</t>
+  </si>
+  <si>
+    <t>Basic implementation lacks depth for scale</t>
+  </si>
+  <si>
+    <t>Enhance objectives with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>BI team members (3-5 people)</t>
+  </si>
+  <si>
+    <t>Documented but inconsistently followed: 1) Teams bypass Premium for 1GB datasets. 2) Exceptions to deployment pipeline standard. 3) Personal gateways installed despite policy. 4) Dataflow-first strategy ignored. 5) Workspace naming not followed. Reference: Governance enforcement.</t>
+  </si>
+  <si>
+    <t>Mature objectives: Documented strategy for capacity, licensing, workspace taxonomy, development lifecycle, gateway architecture, security model, sharing model. Visible in CoE, enforced via tenant settings, monitored via Admin API. Reference: Power BI CoE toolkit.</t>
+  </si>
+  <si>
+    <t>Develop audiences guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Target audiences clearly defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Informal approach leads to inconsistent execution and governance gaps</t>
+  </si>
+  <si>
+    <t>Standardize audiences approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Target audiences clearly defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance audiences with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Target audiences clearly defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal kpis framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI KPIs - KPIs consistently defined: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop kpis guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - KPIs consistently defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize kpis approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - KPIs consistently defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance kpis with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI KPIs consistently defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop ownership guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Business vs IT responsibilities clear: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize ownership approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Business vs IT responsibilities clear: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance ownership with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Business vs IT responsibilities clear acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop demand guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Reporting demand prioritized: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize demand approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Reporting demand prioritized: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance demand with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Reporting demand prioritized acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Standardize naming approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Workspace naming convention: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance naming with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Workspace naming convention acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal environments framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Environments - Dev/Test/Prod separation: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop environments guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Dev/Test/Prod separation: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize environments approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Dev/Test/Prod separation: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance environments with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Dev/Test/Prod separation acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Workspace ownership defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Workspace ownership defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Power BI Workspace ownership defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop governance guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Workspace creation controlled: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize governance approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Workspace creation controlled: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance governance with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Workspace creation controlled acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal production usage framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Production Usage - No production in My Workspace: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop production usage guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - No production in My Workspace: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize production usage approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - No production in My Workspace: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance production usage with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI No production in My Workspace acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal schema design framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Schema Design - Star schema usage: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop schema design guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Star schema usage: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize schema design approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Star schema usage: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance schema design with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Star schema usage acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal reuse framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Reuse - Shared datasets used: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop reuse guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Shared datasets used: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize reuse approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Shared datasets used: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance reuse with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Shared datasets used acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop measures guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Measures centralized and documented: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize measures approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Measures centralized and documented: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance measures with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Measures centralized and documented acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop optimization guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Model size optimized: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize optimization approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Model size optimized: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance optimization with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Model size optimized acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop relationships guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Relationships correctly defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize relationships approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Relationships correctly defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance relationships with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Relationships correctly defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop data inventory guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Data sources documented: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize data inventory approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Data sources documented: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance data inventory with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Data sources documented acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal gateway framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Gateway - Gateway configured and monitored: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop gateway guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Gateway configured and monitored: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize gateway approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Gateway configured and monitored: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance gateway with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Gateway configured and monitored acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop refresh strategy guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Refresh schedules meet business needs: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize refresh strategy approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Refresh schedules meet business needs: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance refresh strategy with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Refresh schedules meet business needs acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal scalability framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Scalability - Incremental refresh used where applicable: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop scalability guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Incremental refresh used where applicable: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize scalability approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Incremental refresh used where applicable: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance scalability with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Incremental refresh used where applicable acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal credentials framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Credentials - Credentials not tied to individuals: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop credentials guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Credentials not tied to individuals: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize credentials approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Credentials not tied to individuals: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance credentials with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Credentials not tied to individuals acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal performance framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Performance - Report performance acceptable: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop performance guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Report performance acceptable: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize performance approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Report performance acceptable: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance performance with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Report performance acceptable acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop dax quality guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - DAX best practices followed: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize dax quality approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - DAX best practices followed: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance dax quality with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI DAX best practices followed acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop ux &amp; visuals guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Visuals optimized and purposeful: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize ux &amp; visuals approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Visuals optimized and purposeful: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance ux &amp; visuals with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Visuals optimized and purposeful acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop query performance guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Query folding preserved: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize query performance approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Query folding preserved: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance query performance with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Query folding preserved acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop storage mode guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Storage mode appropriate: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize storage mode approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Storage mode appropriate: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance storage mode with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Storage mode appropriate acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal access management framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Access Management - Least privilege access applied: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop access management guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Least privilege access applied: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize access management approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Least privilege access applied: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance access management with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Least privilege access applied acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal row-level security framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Row-Level Security - RLS implemented and tested: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop row-level security guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - RLS implemented and tested: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize row-level security approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - RLS implemented and tested: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance row-level security with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI RLS implemented and tested acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop admin rights guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Admin access limited: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize admin rights approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Admin access limited: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance admin rights with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Admin access limited acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop external sharing guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - External sharing controlled: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize external sharing approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - External sharing controlled: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance external sharing with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI External sharing controlled acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Standardize data classification approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Sensitivity labels applied: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance data classification with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Sensitivity labels applied acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal standards framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Standards - Development standards documented: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop standards guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Development standards documented: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize standards approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Development standards documented: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance standards with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Development standards documented acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop version control guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Version control strategy exists: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize version control approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Version control strategy exists: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance version control with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Version control strategy exists acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal deployment framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Deployment - Deployment process defined: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop deployment guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Deployment process defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize deployment approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Deployment process defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance deployment with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Deployment process defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop change management guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Changes are communicated: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize change management approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Changes are communicated: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance change management with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Changes are communicated acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Standardize quality control approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Peer review process exists: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance quality control with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Peer review process exists acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal ownership framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Ownership - Dataset ownership clearly defined: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Dataset ownership clearly defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Dataset ownership clearly defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Power BI Dataset ownership clearly defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal monitoring framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Monitoring - Usage and refresh monitored: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop monitoring guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Usage and refresh monitored: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize monitoring approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Usage and refresh monitored: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance monitoring with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Usage and refresh monitored acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop lifecycle management guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Obsolete reports retired: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize lifecycle management approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Obsolete reports retired: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance lifecycle management with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Obsolete reports retired acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop incident management guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Incident response process exists: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize incident management approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Incident response process exists: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance incident management with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Incident response process exists acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Standardize licensing approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Licensing strategy understood: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance licensing with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Licensing strategy understood acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop training guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Users receive Power BI training: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize training approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Users receive Power BI training: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance training with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Users receive Power BI training acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Standardize documentation approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Documentation accessible: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance documentation with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Documentation accessible acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop support guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Clear support channels exist: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize support approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Clear support channels exist: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance support with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Clear support channels exist acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Standardize feedback approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - User feedback collected: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance feedback with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI User feedback collected acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop adoption metrics guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Adoption metrics tracked: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize adoption metrics approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Adoption metrics tracked: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance adoption metrics with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Adoption metrics tracked acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal strategy framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Strategy - Power BI CoE strategy defined: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop strategy guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Power BI CoE strategy defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize strategy approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Power BI CoE strategy defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance strategy with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Power BI CoE strategy defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal roles framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Roles - CoE roles and responsibilities defined: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop roles guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - CoE roles and responsibilities defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize roles approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - CoE roles and responsibilities defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance roles with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI CoE roles and responsibilities defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Establish formal operating model framework immediately using Power BI best practices</t>
+  </si>
+  <si>
+    <t>Critical gap in Power BI Operating Model - CoE operating model defined: Visible in Admin Portal metrics, prevents using key features (deployment pipelines, shared datasets, RLS), causes governance gaps and audit findings, poor user experience shown in usage metrics. Requires: Admin Portal assessment, documentation, framework implementation, team training, monitoring setup. Reference: Power BI governance frameworks.</t>
+  </si>
+  <si>
+    <t>Develop operating model guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - CoE operating model defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize operating model approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - CoE operating model defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance operating model with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI CoE operating model defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop funding guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - CoE funding model defined: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize funding approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - CoE funding model defined: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance funding with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI CoE funding model defined acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
+  </si>
+  <si>
+    <t>Develop maturity tracking guidelines and configure Power BI settings</t>
+  </si>
+  <si>
+    <t>Significant Power BI gap - Maturity tracked over time: Reduces efficiency, inconsistent across workspaces/datasets, growing technical debt, suboptimal Premium capacity usage (check Admin Portal &gt; Capacity metrics), scaling difficulties. Address: document standards, create templates, train team, implement monitoring. Reference: Power BI best practices.</t>
+  </si>
+  <si>
+    <t>Standardize maturity tracking approach with templates and monitoring</t>
+  </si>
+  <si>
+    <t>Moderate Power BI gap - Maturity tracked over time: Basic functionality works but not optimized, some inconsistency, manual processes could use Power BI APIs, limited monitoring, missing advanced features. Improve: standardize, document, enhance Admin Portal monitoring. Reference: Power BI optimization guides.</t>
+  </si>
+  <si>
+    <t>Enhance maturity tracking with Admin Portal monitoring</t>
+  </si>
+  <si>
+    <t>Power BI Maturity tracked over time acceptable with optimization opportunities: Could benefit from automation via REST API/PowerShell, better documentation, comprehensive Admin Portal monitoring, advanced features exploration (composite models, aggregations, calculation groups, incremental refresh). Reference: Power BI advanced features.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2432,8 +3434,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2452,8 +3460,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2485,11 +3499,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2497,6 +3526,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2550,10 +3585,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2900,7 +3931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEA3D0E-31EC-440A-A0FE-216444E746F8}">
-  <dimension ref="A1:N251"/>
+  <dimension ref="A1:R251"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2914,9 +3945,12 @@
     <col min="12" max="12" width="52.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5546875" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="15" max="16" width="120" customWidth="1"/>
+    <col min="17" max="17" width="35" customWidth="1"/>
+    <col min="18" max="18" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -2959,8 +3993,20 @@
       <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -3005,8 +4051,20 @@
         <f t="array" ref="N2">_xlfn.SWITCH(M2,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>790</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -3051,8 +4109,20 @@
         <f t="array" ref="N3">_xlfn.SWITCH(M3,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>794</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -3097,8 +4167,20 @@
         <f t="array" ref="N4">_xlfn.SWITCH(M4,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>798</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -3143,8 +4225,20 @@
         <f t="array" ref="N5">_xlfn.SWITCH(M5,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>802</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -3189,8 +4283,20 @@
         <f t="array" ref="N6">_xlfn.SWITCH(M6,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>802</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -3235,8 +4341,20 @@
         <f t="array" ref="N7">_xlfn.SWITCH(M7,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>794</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>94</v>
       </c>
@@ -3281,8 +4399,20 @@
         <f t="array" ref="N8">_xlfn.SWITCH(M8,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>798</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -3327,8 +4457,20 @@
         <f t="array" ref="N9">_xlfn.SWITCH(M9,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>798</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -3373,8 +4515,20 @@
         <f t="array" ref="N10">_xlfn.SWITCH(M10,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>802</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
@@ -3419,8 +4573,20 @@
         <f t="array" ref="N11">_xlfn.SWITCH(M11,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>802</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -3465,8 +4631,20 @@
         <f t="array" ref="N12">_xlfn.SWITCH(M12,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>790</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -3511,8 +4689,20 @@
         <f t="array" ref="N13">_xlfn.SWITCH(M13,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>794</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -3557,8 +4747,20 @@
         <f t="array" ref="N14">_xlfn.SWITCH(M14,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>798</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -3603,8 +4805,20 @@
         <f t="array" ref="N15">_xlfn.SWITCH(M15,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>802</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -3649,8 +4863,20 @@
         <f t="array" ref="N16">_xlfn.SWITCH(M16,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>802</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -3695,8 +4921,20 @@
         <f t="array" ref="N17">_xlfn.SWITCH(M17,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>794</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -3741,8 +4979,20 @@
         <f t="array" ref="N18">_xlfn.SWITCH(M18,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>798</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -3787,8 +5037,20 @@
         <f t="array" ref="N19">_xlfn.SWITCH(M19,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>798</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -3833,8 +5095,20 @@
         <f t="array" ref="N20">_xlfn.SWITCH(M20,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>802</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -3879,8 +5153,20 @@
         <f t="array" ref="N21">_xlfn.SWITCH(M21,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>802</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -3925,8 +5211,20 @@
         <f t="array" ref="N22">_xlfn.SWITCH(M22,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>794</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -3971,8 +5269,20 @@
         <f t="array" ref="N23">_xlfn.SWITCH(M23,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>798</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -4017,8 +5327,20 @@
         <f t="array" ref="N24">_xlfn.SWITCH(M24,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>798</v>
+      </c>
+      <c r="R24" s="5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -4063,8 +5385,20 @@
         <f t="array" ref="N25">_xlfn.SWITCH(M25,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>802</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -4109,8 +5443,20 @@
         <f t="array" ref="N26">_xlfn.SWITCH(M26,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>802</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>132</v>
       </c>
@@ -4155,8 +5501,20 @@
         <f t="array" ref="N27">_xlfn.SWITCH(M27,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>798</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>132</v>
       </c>
@@ -4201,8 +5559,20 @@
         <f t="array" ref="N28">_xlfn.SWITCH(M28,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>802</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>132</v>
       </c>
@@ -4247,8 +5617,20 @@
         <f t="array" ref="N29">_xlfn.SWITCH(M29,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>802</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>132</v>
       </c>
@@ -4293,8 +5675,20 @@
         <f t="array" ref="N30">_xlfn.SWITCH(M30,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>802</v>
+      </c>
+      <c r="R30" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -4339,8 +5733,20 @@
         <f t="array" ref="N31">_xlfn.SWITCH(M31,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>802</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -4385,8 +5791,20 @@
         <f t="array" ref="N32">_xlfn.SWITCH(M32,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>790</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>132</v>
       </c>
@@ -4431,8 +5849,20 @@
         <f t="array" ref="N33">_xlfn.SWITCH(M33,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>794</v>
+      </c>
+      <c r="R33" s="5" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>132</v>
       </c>
@@ -4477,8 +5907,20 @@
         <f t="array" ref="N34">_xlfn.SWITCH(M34,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P34" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>798</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>132</v>
       </c>
@@ -4523,8 +5965,20 @@
         <f t="array" ref="N35">_xlfn.SWITCH(M35,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>802</v>
+      </c>
+      <c r="R35" s="5" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -4569,8 +6023,20 @@
         <f t="array" ref="N36">_xlfn.SWITCH(M36,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P36" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>802</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -4615,8 +6081,20 @@
         <f t="array" ref="N37">_xlfn.SWITCH(M37,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P37" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>794</v>
+      </c>
+      <c r="R37" s="5" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -4661,8 +6139,20 @@
         <f t="array" ref="N38">_xlfn.SWITCH(M38,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>798</v>
+      </c>
+      <c r="R38" s="5" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>132</v>
       </c>
@@ -4707,8 +6197,20 @@
         <f t="array" ref="N39">_xlfn.SWITCH(M39,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>798</v>
+      </c>
+      <c r="R39" s="5" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>132</v>
       </c>
@@ -4753,8 +6255,20 @@
         <f t="array" ref="N40">_xlfn.SWITCH(M40,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>802</v>
+      </c>
+      <c r="R40" s="5" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>132</v>
       </c>
@@ -4799,8 +6313,20 @@
         <f t="array" ref="N41">_xlfn.SWITCH(M41,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>802</v>
+      </c>
+      <c r="R41" s="5" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>132</v>
       </c>
@@ -4845,8 +6371,20 @@
         <f t="array" ref="N42">_xlfn.SWITCH(M42,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>794</v>
+      </c>
+      <c r="R42" s="5" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>132</v>
       </c>
@@ -4891,8 +6429,20 @@
         <f t="array" ref="N43">_xlfn.SWITCH(M43,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>798</v>
+      </c>
+      <c r="R43" s="5" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>132</v>
       </c>
@@ -4937,8 +6487,20 @@
         <f t="array" ref="N44">_xlfn.SWITCH(M44,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>798</v>
+      </c>
+      <c r="R44" s="5" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -4983,8 +6545,20 @@
         <f t="array" ref="N45">_xlfn.SWITCH(M45,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>802</v>
+      </c>
+      <c r="R45" s="5" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -5029,8 +6603,20 @@
         <f t="array" ref="N46">_xlfn.SWITCH(M46,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>802</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>132</v>
       </c>
@@ -5075,8 +6661,20 @@
         <f t="array" ref="N47">_xlfn.SWITCH(M47,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P47" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>790</v>
+      </c>
+      <c r="R47" s="5" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>132</v>
       </c>
@@ -5121,8 +6719,20 @@
         <f t="array" ref="N48">_xlfn.SWITCH(M48,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O48" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P48" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>794</v>
+      </c>
+      <c r="R48" s="5" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>132</v>
       </c>
@@ -5167,8 +6777,20 @@
         <f t="array" ref="N49">_xlfn.SWITCH(M49,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O49" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P49" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>798</v>
+      </c>
+      <c r="R49" s="5" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>132</v>
       </c>
@@ -5213,8 +6835,20 @@
         <f t="array" ref="N50">_xlfn.SWITCH(M50,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O50" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P50" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>802</v>
+      </c>
+      <c r="R50" s="5" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>132</v>
       </c>
@@ -5259,8 +6893,20 @@
         <f t="array" ref="N51">_xlfn.SWITCH(M51,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O51" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P51" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>802</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>169</v>
       </c>
@@ -5305,8 +6951,20 @@
         <f t="array" ref="N52">_xlfn.SWITCH(M52,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O52" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P52" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>790</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>169</v>
       </c>
@@ -5351,8 +7009,20 @@
         <f t="array" ref="N53">_xlfn.SWITCH(M53,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O53" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P53" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>794</v>
+      </c>
+      <c r="R53" s="5" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>169</v>
       </c>
@@ -5397,8 +7067,20 @@
         <f t="array" ref="N54">_xlfn.SWITCH(M54,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O54" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P54" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>798</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>169</v>
       </c>
@@ -5443,8 +7125,20 @@
         <f t="array" ref="N55">_xlfn.SWITCH(M55,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O55" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P55" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>802</v>
+      </c>
+      <c r="R55" s="5" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>169</v>
       </c>
@@ -5489,8 +7183,20 @@
         <f t="array" ref="N56">_xlfn.SWITCH(M56,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O56" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P56" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>802</v>
+      </c>
+      <c r="R56" s="5" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>169</v>
       </c>
@@ -5535,8 +7241,20 @@
         <f t="array" ref="N57">_xlfn.SWITCH(M57,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O57" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P57" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>790</v>
+      </c>
+      <c r="R57" s="5" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>169</v>
       </c>
@@ -5581,8 +7299,20 @@
         <f t="array" ref="N58">_xlfn.SWITCH(M58,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O58" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P58" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>794</v>
+      </c>
+      <c r="R58" s="5" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -5627,8 +7357,20 @@
         <f t="array" ref="N59">_xlfn.SWITCH(M59,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O59" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P59" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>798</v>
+      </c>
+      <c r="R59" s="5" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>169</v>
       </c>
@@ -5673,8 +7415,20 @@
         <f t="array" ref="N60">_xlfn.SWITCH(M60,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O60" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P60" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>802</v>
+      </c>
+      <c r="R60" s="5" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>169</v>
       </c>
@@ -5719,8 +7473,20 @@
         <f t="array" ref="N61">_xlfn.SWITCH(M61,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O61" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P61" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>802</v>
+      </c>
+      <c r="R61" s="5" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -5765,8 +7531,20 @@
         <f t="array" ref="N62">_xlfn.SWITCH(M62,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O62" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P62" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>794</v>
+      </c>
+      <c r="R62" s="5" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>169</v>
       </c>
@@ -5811,8 +7589,20 @@
         <f t="array" ref="N63">_xlfn.SWITCH(M63,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O63" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P63" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>798</v>
+      </c>
+      <c r="R63" s="5" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>169</v>
       </c>
@@ -5857,8 +7647,20 @@
         <f t="array" ref="N64">_xlfn.SWITCH(M64,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O64" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P64" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>798</v>
+      </c>
+      <c r="R64" s="5" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>169</v>
       </c>
@@ -5903,8 +7705,20 @@
         <f t="array" ref="N65">_xlfn.SWITCH(M65,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O65" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P65" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>802</v>
+      </c>
+      <c r="R65" s="5" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>169</v>
       </c>
@@ -5949,8 +7763,20 @@
         <f t="array" ref="N66">_xlfn.SWITCH(M66,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O66" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P66" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>802</v>
+      </c>
+      <c r="R66" s="5" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>169</v>
       </c>
@@ -5995,8 +7821,20 @@
         <f t="array" ref="N67">_xlfn.SWITCH(M67,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O67" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P67" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>794</v>
+      </c>
+      <c r="R67" s="5" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>169</v>
       </c>
@@ -6041,8 +7879,20 @@
         <f t="array" ref="N68">_xlfn.SWITCH(M68,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O68" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P68" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>798</v>
+      </c>
+      <c r="R68" s="5" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>169</v>
       </c>
@@ -6087,8 +7937,20 @@
         <f t="array" ref="N69">_xlfn.SWITCH(M69,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P69" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>798</v>
+      </c>
+      <c r="R69" s="5" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>169</v>
       </c>
@@ -6133,8 +7995,20 @@
         <f t="array" ref="N70">_xlfn.SWITCH(M70,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O70" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P70" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>802</v>
+      </c>
+      <c r="R70" s="5" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>169</v>
       </c>
@@ -6179,8 +8053,20 @@
         <f t="array" ref="N71">_xlfn.SWITCH(M71,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P71" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>802</v>
+      </c>
+      <c r="R71" s="5" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>169</v>
       </c>
@@ -6225,8 +8111,20 @@
         <f t="array" ref="N72">_xlfn.SWITCH(M72,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O72" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P72" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>794</v>
+      </c>
+      <c r="R72" s="5" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>169</v>
       </c>
@@ -6271,8 +8169,20 @@
         <f t="array" ref="N73">_xlfn.SWITCH(M73,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O73" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P73" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>798</v>
+      </c>
+      <c r="R73" s="5" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>169</v>
       </c>
@@ -6317,8 +8227,20 @@
         <f t="array" ref="N74">_xlfn.SWITCH(M74,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P74" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>798</v>
+      </c>
+      <c r="R74" s="5" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>169</v>
       </c>
@@ -6363,8 +8285,20 @@
         <f t="array" ref="N75">_xlfn.SWITCH(M75,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O75" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P75" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>802</v>
+      </c>
+      <c r="R75" s="5" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>169</v>
       </c>
@@ -6409,8 +8343,20 @@
         <f t="array" ref="N76">_xlfn.SWITCH(M76,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O76" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P76" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>802</v>
+      </c>
+      <c r="R76" s="5" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>247</v>
       </c>
@@ -6455,8 +8401,20 @@
         <f t="array" ref="N77">_xlfn.SWITCH(M77,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O77" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P77" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>794</v>
+      </c>
+      <c r="R77" s="5" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>247</v>
       </c>
@@ -6501,8 +8459,20 @@
         <f t="array" ref="N78">_xlfn.SWITCH(M78,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O78" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P78" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>798</v>
+      </c>
+      <c r="R78" s="5" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>247</v>
       </c>
@@ -6547,8 +8517,20 @@
         <f t="array" ref="N79">_xlfn.SWITCH(M79,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O79" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P79" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>798</v>
+      </c>
+      <c r="R79" s="5" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>247</v>
       </c>
@@ -6593,8 +8575,20 @@
         <f t="array" ref="N80">_xlfn.SWITCH(M80,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P80" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>802</v>
+      </c>
+      <c r="R80" s="5" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>247</v>
       </c>
@@ -6639,8 +8633,20 @@
         <f t="array" ref="N81">_xlfn.SWITCH(M81,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P81" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>802</v>
+      </c>
+      <c r="R81" s="5" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>247</v>
       </c>
@@ -6685,8 +8691,20 @@
         <f t="array" ref="N82">_xlfn.SWITCH(M82,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P82" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>790</v>
+      </c>
+      <c r="R82" s="5" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>247</v>
       </c>
@@ -6731,8 +8749,20 @@
         <f t="array" ref="N83">_xlfn.SWITCH(M83,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O83" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P83" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>794</v>
+      </c>
+      <c r="R83" s="5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>247</v>
       </c>
@@ -6777,8 +8807,20 @@
         <f t="array" ref="N84">_xlfn.SWITCH(M84,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O84" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="P84" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>798</v>
+      </c>
+      <c r="R84" s="5" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>247</v>
       </c>
@@ -6823,8 +8865,20 @@
         <f t="array" ref="N85">_xlfn.SWITCH(M85,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O85" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P85" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>802</v>
+      </c>
+      <c r="R85" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>247</v>
       </c>
@@ -6869,8 +8923,20 @@
         <f t="array" ref="N86">_xlfn.SWITCH(M86,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O86" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P86" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>802</v>
+      </c>
+      <c r="R86" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>247</v>
       </c>
@@ -6915,8 +8981,20 @@
         <f t="array" ref="N87">_xlfn.SWITCH(M87,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O87" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P87" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>794</v>
+      </c>
+      <c r="R87" s="5" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>247</v>
       </c>
@@ -6961,8 +9039,20 @@
         <f t="array" ref="N88">_xlfn.SWITCH(M88,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O88" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P88" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>798</v>
+      </c>
+      <c r="R88" s="5" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>247</v>
       </c>
@@ -7007,8 +9097,20 @@
         <f t="array" ref="N89">_xlfn.SWITCH(M89,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O89" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P89" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>798</v>
+      </c>
+      <c r="R89" s="5" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>247</v>
       </c>
@@ -7053,8 +9155,20 @@
         <f t="array" ref="N90">_xlfn.SWITCH(M90,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O90" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P90" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>802</v>
+      </c>
+      <c r="R90" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>247</v>
       </c>
@@ -7099,8 +9213,20 @@
         <f t="array" ref="N91">_xlfn.SWITCH(M91,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O91" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P91" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>802</v>
+      </c>
+      <c r="R91" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>247</v>
       </c>
@@ -7145,8 +9271,20 @@
         <f t="array" ref="N92">_xlfn.SWITCH(M92,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O92" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P92" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>790</v>
+      </c>
+      <c r="R92" s="5" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>247</v>
       </c>
@@ -7191,8 +9329,20 @@
         <f t="array" ref="N93">_xlfn.SWITCH(M93,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O93" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P93" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>794</v>
+      </c>
+      <c r="R93" s="5" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>247</v>
       </c>
@@ -7237,8 +9387,20 @@
         <f t="array" ref="N94">_xlfn.SWITCH(M94,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O94" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P94" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>798</v>
+      </c>
+      <c r="R94" s="5" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>247</v>
       </c>
@@ -7283,8 +9445,20 @@
         <f t="array" ref="N95">_xlfn.SWITCH(M95,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O95" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P95" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>802</v>
+      </c>
+      <c r="R95" s="5" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>247</v>
       </c>
@@ -7329,8 +9503,20 @@
         <f t="array" ref="N96">_xlfn.SWITCH(M96,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O96" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P96" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>802</v>
+      </c>
+      <c r="R96" s="5" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>247</v>
       </c>
@@ -7375,8 +9561,20 @@
         <f t="array" ref="N97">_xlfn.SWITCH(M97,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O97" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P97" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>790</v>
+      </c>
+      <c r="R97" s="5" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>247</v>
       </c>
@@ -7421,8 +9619,20 @@
         <f t="array" ref="N98">_xlfn.SWITCH(M98,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O98" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P98" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>794</v>
+      </c>
+      <c r="R98" s="5" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>247</v>
       </c>
@@ -7467,8 +9677,20 @@
         <f t="array" ref="N99">_xlfn.SWITCH(M99,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O99" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P99" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>798</v>
+      </c>
+      <c r="R99" s="5" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>247</v>
       </c>
@@ -7513,8 +9735,20 @@
         <f t="array" ref="N100">_xlfn.SWITCH(M100,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O100" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P100" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>802</v>
+      </c>
+      <c r="R100" s="5" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>247</v>
       </c>
@@ -7559,8 +9793,20 @@
         <f t="array" ref="N101">_xlfn.SWITCH(M101,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O101" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P101" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>802</v>
+      </c>
+      <c r="R101" s="5" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>324</v>
       </c>
@@ -7605,8 +9851,20 @@
         <f t="array" ref="N102">_xlfn.SWITCH(M102,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O102" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P102" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>790</v>
+      </c>
+      <c r="R102" s="5" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>324</v>
       </c>
@@ -7651,8 +9909,20 @@
         <f t="array" ref="N103">_xlfn.SWITCH(M103,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O103" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P103" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>794</v>
+      </c>
+      <c r="R103" s="5" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>324</v>
       </c>
@@ -7697,8 +9967,20 @@
         <f t="array" ref="N104">_xlfn.SWITCH(M104,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O104" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P104" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>798</v>
+      </c>
+      <c r="R104" s="5" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>324</v>
       </c>
@@ -7743,8 +10025,20 @@
         <f t="array" ref="N105">_xlfn.SWITCH(M105,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O105" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P105" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>802</v>
+      </c>
+      <c r="R105" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>324</v>
       </c>
@@ -7789,8 +10083,20 @@
         <f t="array" ref="N106">_xlfn.SWITCH(M106,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O106" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P106" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>802</v>
+      </c>
+      <c r="R106" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>324</v>
       </c>
@@ -7835,8 +10141,20 @@
         <f t="array" ref="N107">_xlfn.SWITCH(M107,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O107" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P107" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>794</v>
+      </c>
+      <c r="R107" s="5" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>324</v>
       </c>
@@ -7881,8 +10199,20 @@
         <f t="array" ref="N108">_xlfn.SWITCH(M108,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O108" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P108" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>798</v>
+      </c>
+      <c r="R108" s="5" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>324</v>
       </c>
@@ -7927,8 +10257,20 @@
         <f t="array" ref="N109">_xlfn.SWITCH(M109,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O109" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P109" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>798</v>
+      </c>
+      <c r="R109" s="5" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>324</v>
       </c>
@@ -7973,8 +10315,20 @@
         <f t="array" ref="N110">_xlfn.SWITCH(M110,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P110" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>802</v>
+      </c>
+      <c r="R110" s="5" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>324</v>
       </c>
@@ -8019,8 +10373,20 @@
         <f t="array" ref="N111">_xlfn.SWITCH(M111,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O111" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P111" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>802</v>
+      </c>
+      <c r="R111" s="5" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>324</v>
       </c>
@@ -8065,8 +10431,20 @@
         <f t="array" ref="N112">_xlfn.SWITCH(M112,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O112" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P112" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>794</v>
+      </c>
+      <c r="R112" s="5" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>324</v>
       </c>
@@ -8111,8 +10489,20 @@
         <f t="array" ref="N113">_xlfn.SWITCH(M113,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O113" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P113" s="5" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>798</v>
+      </c>
+      <c r="R113" s="5" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>324</v>
       </c>
@@ -8157,8 +10547,20 @@
         <f t="array" ref="N114">_xlfn.SWITCH(M114,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O114" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P114" s="5" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>798</v>
+      </c>
+      <c r="R114" s="5" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>324</v>
       </c>
@@ -8203,8 +10605,20 @@
         <f t="array" ref="N115">_xlfn.SWITCH(M115,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O115" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P115" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>802</v>
+      </c>
+      <c r="R115" s="5" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>324</v>
       </c>
@@ -8249,8 +10663,20 @@
         <f t="array" ref="N116">_xlfn.SWITCH(M116,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O116" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P116" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>802</v>
+      </c>
+      <c r="R116" s="5" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>324</v>
       </c>
@@ -8295,8 +10721,20 @@
         <f t="array" ref="N117">_xlfn.SWITCH(M117,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O117" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P117" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>794</v>
+      </c>
+      <c r="R117" s="5" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>324</v>
       </c>
@@ -8341,8 +10779,20 @@
         <f t="array" ref="N118">_xlfn.SWITCH(M118,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O118" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P118" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>798</v>
+      </c>
+      <c r="R118" s="5" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>324</v>
       </c>
@@ -8387,8 +10837,20 @@
         <f t="array" ref="N119">_xlfn.SWITCH(M119,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O119" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P119" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>798</v>
+      </c>
+      <c r="R119" s="5" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>324</v>
       </c>
@@ -8433,8 +10895,20 @@
         <f t="array" ref="N120">_xlfn.SWITCH(M120,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O120" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P120" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>802</v>
+      </c>
+      <c r="R120" s="5" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>324</v>
       </c>
@@ -8479,8 +10953,20 @@
         <f t="array" ref="N121">_xlfn.SWITCH(M121,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O121" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P121" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>802</v>
+      </c>
+      <c r="R121" s="5" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>324</v>
       </c>
@@ -8525,8 +11011,20 @@
         <f t="array" ref="N122">_xlfn.SWITCH(M122,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O122" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P122" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>794</v>
+      </c>
+      <c r="R122" s="5" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>324</v>
       </c>
@@ -8571,8 +11069,20 @@
         <f t="array" ref="N123">_xlfn.SWITCH(M123,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O123" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P123" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>798</v>
+      </c>
+      <c r="R123" s="5" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>324</v>
       </c>
@@ -8617,8 +11127,20 @@
         <f t="array" ref="N124">_xlfn.SWITCH(M124,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O124" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="P124" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>798</v>
+      </c>
+      <c r="R124" s="5" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>324</v>
       </c>
@@ -8663,8 +11185,20 @@
         <f t="array" ref="N125">_xlfn.SWITCH(M125,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O125" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P125" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>802</v>
+      </c>
+      <c r="R125" s="5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>324</v>
       </c>
@@ -8709,8 +11243,20 @@
         <f t="array" ref="N126">_xlfn.SWITCH(M126,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O126" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P126" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>802</v>
+      </c>
+      <c r="R126" s="5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>401</v>
       </c>
@@ -8755,8 +11301,20 @@
         <f t="array" ref="N127">_xlfn.SWITCH(M127,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O127" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P127" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>790</v>
+      </c>
+      <c r="R127" s="5" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>401</v>
       </c>
@@ -8801,8 +11359,20 @@
         <f t="array" ref="N128">_xlfn.SWITCH(M128,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O128" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P128" s="5" t="s">
+        <v>965</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>794</v>
+      </c>
+      <c r="R128" s="5" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>401</v>
       </c>
@@ -8847,8 +11417,20 @@
         <f t="array" ref="N129">_xlfn.SWITCH(M129,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O129" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P129" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>798</v>
+      </c>
+      <c r="R129" s="5" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>401</v>
       </c>
@@ -8893,8 +11475,20 @@
         <f t="array" ref="N130">_xlfn.SWITCH(M130,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O130" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P130" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>802</v>
+      </c>
+      <c r="R130" s="5" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>401</v>
       </c>
@@ -8939,8 +11533,20 @@
         <f t="array" ref="N131">_xlfn.SWITCH(M131,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O131" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P131" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>802</v>
+      </c>
+      <c r="R131" s="5" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>401</v>
       </c>
@@ -8985,8 +11591,20 @@
         <f t="array" ref="N132">_xlfn.SWITCH(M132,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O132" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P132" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>790</v>
+      </c>
+      <c r="R132" s="5" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>401</v>
       </c>
@@ -9031,8 +11649,20 @@
         <f t="array" ref="N133">_xlfn.SWITCH(M133,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O133" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P133" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>794</v>
+      </c>
+      <c r="R133" s="5" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>401</v>
       </c>
@@ -9077,8 +11707,20 @@
         <f t="array" ref="N134">_xlfn.SWITCH(M134,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O134" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P134" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>798</v>
+      </c>
+      <c r="R134" s="5" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>401</v>
       </c>
@@ -9123,8 +11765,20 @@
         <f t="array" ref="N135">_xlfn.SWITCH(M135,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O135" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P135" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>802</v>
+      </c>
+      <c r="R135" s="5" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>401</v>
       </c>
@@ -9169,8 +11823,20 @@
         <f t="array" ref="N136">_xlfn.SWITCH(M136,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O136" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P136" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>802</v>
+      </c>
+      <c r="R136" s="5" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>401</v>
       </c>
@@ -9215,8 +11881,20 @@
         <f t="array" ref="N137">_xlfn.SWITCH(M137,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O137" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P137" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>794</v>
+      </c>
+      <c r="R137" s="5" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>401</v>
       </c>
@@ -9261,8 +11939,20 @@
         <f t="array" ref="N138">_xlfn.SWITCH(M138,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O138" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P138" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>798</v>
+      </c>
+      <c r="R138" s="5" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>401</v>
       </c>
@@ -9307,8 +11997,20 @@
         <f t="array" ref="N139">_xlfn.SWITCH(M139,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O139" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P139" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>798</v>
+      </c>
+      <c r="R139" s="5" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>401</v>
       </c>
@@ -9353,8 +12055,20 @@
         <f t="array" ref="N140">_xlfn.SWITCH(M140,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O140" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P140" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>802</v>
+      </c>
+      <c r="R140" s="5" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>401</v>
       </c>
@@ -9399,8 +12113,20 @@
         <f t="array" ref="N141">_xlfn.SWITCH(M141,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O141" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P141" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>802</v>
+      </c>
+      <c r="R141" s="5" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>401</v>
       </c>
@@ -9445,8 +12171,20 @@
         <f t="array" ref="N142">_xlfn.SWITCH(M142,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O142" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P142" s="5" t="s">
+        <v>985</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>794</v>
+      </c>
+      <c r="R142" s="5" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>401</v>
       </c>
@@ -9491,8 +12229,20 @@
         <f t="array" ref="N143">_xlfn.SWITCH(M143,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O143" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P143" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>798</v>
+      </c>
+      <c r="R143" s="5" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>401</v>
       </c>
@@ -9537,8 +12287,20 @@
         <f t="array" ref="N144">_xlfn.SWITCH(M144,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O144" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P144" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>798</v>
+      </c>
+      <c r="R144" s="5" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>401</v>
       </c>
@@ -9583,8 +12345,20 @@
         <f t="array" ref="N145">_xlfn.SWITCH(M145,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O145" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P145" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>802</v>
+      </c>
+      <c r="R145" s="5" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>401</v>
       </c>
@@ -9629,8 +12403,20 @@
         <f t="array" ref="N146">_xlfn.SWITCH(M146,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O146" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P146" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>802</v>
+      </c>
+      <c r="R146" s="5" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>401</v>
       </c>
@@ -9675,8 +12461,20 @@
         <f t="array" ref="N147">_xlfn.SWITCH(M147,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O147" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P147" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>798</v>
+      </c>
+      <c r="R147" s="5" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>401</v>
       </c>
@@ -9721,8 +12519,20 @@
         <f t="array" ref="N148">_xlfn.SWITCH(M148,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O148" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P148" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>802</v>
+      </c>
+      <c r="R148" s="5" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>401</v>
       </c>
@@ -9767,8 +12577,20 @@
         <f t="array" ref="N149">_xlfn.SWITCH(M149,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O149" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P149" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>802</v>
+      </c>
+      <c r="R149" s="5" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>401</v>
       </c>
@@ -9813,8 +12635,20 @@
         <f t="array" ref="N150">_xlfn.SWITCH(M150,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O150" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P150" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>802</v>
+      </c>
+      <c r="R150" s="5" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>401</v>
       </c>
@@ -9859,8 +12693,20 @@
         <f t="array" ref="N151">_xlfn.SWITCH(M151,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O151" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P151" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>802</v>
+      </c>
+      <c r="R151" s="5" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>478</v>
       </c>
@@ -9905,8 +12751,20 @@
         <f t="array" ref="N152">_xlfn.SWITCH(M152,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O152" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P152" s="5" t="s">
+        <v>995</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>790</v>
+      </c>
+      <c r="R152" s="5" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>478</v>
       </c>
@@ -9951,8 +12809,20 @@
         <f t="array" ref="N153">_xlfn.SWITCH(M153,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O153" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P153" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>794</v>
+      </c>
+      <c r="R153" s="5" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>478</v>
       </c>
@@ -9997,8 +12867,20 @@
         <f t="array" ref="N154">_xlfn.SWITCH(M154,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O154" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P154" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>798</v>
+      </c>
+      <c r="R154" s="5" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>478</v>
       </c>
@@ -10043,8 +12925,20 @@
         <f t="array" ref="N155">_xlfn.SWITCH(M155,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O155" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P155" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>802</v>
+      </c>
+      <c r="R155" s="5" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>478</v>
       </c>
@@ -10089,8 +12983,20 @@
         <f t="array" ref="N156">_xlfn.SWITCH(M156,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O156" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P156" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>802</v>
+      </c>
+      <c r="R156" s="5" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>478</v>
       </c>
@@ -10135,8 +13041,20 @@
         <f t="array" ref="N157">_xlfn.SWITCH(M157,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O157" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P157" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>794</v>
+      </c>
+      <c r="R157" s="5" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>478</v>
       </c>
@@ -10181,8 +13099,20 @@
         <f t="array" ref="N158">_xlfn.SWITCH(M158,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O158" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P158" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>798</v>
+      </c>
+      <c r="R158" s="5" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>478</v>
       </c>
@@ -10227,8 +13157,20 @@
         <f t="array" ref="N159">_xlfn.SWITCH(M159,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O159" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P159" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>798</v>
+      </c>
+      <c r="R159" s="5" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>478</v>
       </c>
@@ -10273,8 +13215,20 @@
         <f t="array" ref="N160">_xlfn.SWITCH(M160,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O160" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P160" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>802</v>
+      </c>
+      <c r="R160" s="5" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>478</v>
       </c>
@@ -10319,8 +13273,20 @@
         <f t="array" ref="N161">_xlfn.SWITCH(M161,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O161" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P161" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>802</v>
+      </c>
+      <c r="R161" s="5" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>478</v>
       </c>
@@ -10365,8 +13331,20 @@
         <f t="array" ref="N162">_xlfn.SWITCH(M162,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O162" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P162" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>790</v>
+      </c>
+      <c r="R162" s="5" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>478</v>
       </c>
@@ -10411,8 +13389,20 @@
         <f t="array" ref="N163">_xlfn.SWITCH(M163,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O163" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P163" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>794</v>
+      </c>
+      <c r="R163" s="5" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>478</v>
       </c>
@@ -10457,8 +13447,20 @@
         <f t="array" ref="N164">_xlfn.SWITCH(M164,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O164" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P164" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>798</v>
+      </c>
+      <c r="R164" s="5" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>478</v>
       </c>
@@ -10503,8 +13505,20 @@
         <f t="array" ref="N165">_xlfn.SWITCH(M165,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O165" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P165" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>802</v>
+      </c>
+      <c r="R165" s="5" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>478</v>
       </c>
@@ -10549,8 +13563,20 @@
         <f t="array" ref="N166">_xlfn.SWITCH(M166,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O166" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P166" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>802</v>
+      </c>
+      <c r="R166" s="5" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>478</v>
       </c>
@@ -10595,8 +13621,20 @@
         <f t="array" ref="N167">_xlfn.SWITCH(M167,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O167" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P167" s="5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>794</v>
+      </c>
+      <c r="R167" s="5" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>478</v>
       </c>
@@ -10641,8 +13679,20 @@
         <f t="array" ref="N168">_xlfn.SWITCH(M168,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O168" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P168" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>798</v>
+      </c>
+      <c r="R168" s="5" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>478</v>
       </c>
@@ -10687,8 +13737,20 @@
         <f t="array" ref="N169">_xlfn.SWITCH(M169,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O169" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P169" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>798</v>
+      </c>
+      <c r="R169" s="5" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>478</v>
       </c>
@@ -10733,8 +13795,20 @@
         <f t="array" ref="N170">_xlfn.SWITCH(M170,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O170" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P170" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>802</v>
+      </c>
+      <c r="R170" s="5" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>478</v>
       </c>
@@ -10779,8 +13853,20 @@
         <f t="array" ref="N171">_xlfn.SWITCH(M171,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O171" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P171" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>802</v>
+      </c>
+      <c r="R171" s="5" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>478</v>
       </c>
@@ -10825,8 +13911,20 @@
         <f t="array" ref="N172">_xlfn.SWITCH(M172,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O172" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P172" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>798</v>
+      </c>
+      <c r="R172" s="5" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>478</v>
       </c>
@@ -10871,8 +13969,20 @@
         <f t="array" ref="N173">_xlfn.SWITCH(M173,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O173" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P173" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>802</v>
+      </c>
+      <c r="R173" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>478</v>
       </c>
@@ -10917,8 +14027,20 @@
         <f t="array" ref="N174">_xlfn.SWITCH(M174,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P174" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>802</v>
+      </c>
+      <c r="R174" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>478</v>
       </c>
@@ -10963,8 +14085,20 @@
         <f t="array" ref="N175">_xlfn.SWITCH(M175,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P175" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>802</v>
+      </c>
+      <c r="R175" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>478</v>
       </c>
@@ -11009,8 +14143,20 @@
         <f t="array" ref="N176">_xlfn.SWITCH(M176,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O176" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P176" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>802</v>
+      </c>
+      <c r="R176" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>555</v>
       </c>
@@ -11055,8 +14201,20 @@
         <f t="array" ref="N177">_xlfn.SWITCH(M177,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O177" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P177" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>790</v>
+      </c>
+      <c r="R177" s="5" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>555</v>
       </c>
@@ -11101,8 +14259,20 @@
         <f t="array" ref="N178">_xlfn.SWITCH(M178,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O178" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P178" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>794</v>
+      </c>
+      <c r="R178" s="5" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>555</v>
       </c>
@@ -11147,8 +14317,20 @@
         <f t="array" ref="N179">_xlfn.SWITCH(M179,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O179" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P179" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>798</v>
+      </c>
+      <c r="R179" s="5" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>555</v>
       </c>
@@ -11193,8 +14375,20 @@
         <f t="array" ref="N180">_xlfn.SWITCH(M180,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O180" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P180" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>802</v>
+      </c>
+      <c r="R180" s="5" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>555</v>
       </c>
@@ -11239,8 +14433,20 @@
         <f t="array" ref="N181">_xlfn.SWITCH(M181,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O181" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P181" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>802</v>
+      </c>
+      <c r="R181" s="5" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>555</v>
       </c>
@@ -11285,8 +14491,20 @@
         <f t="array" ref="N182">_xlfn.SWITCH(M182,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O182" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P182" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>790</v>
+      </c>
+      <c r="R182" s="5" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>555</v>
       </c>
@@ -11331,8 +14549,20 @@
         <f t="array" ref="N183">_xlfn.SWITCH(M183,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O183" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P183" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>794</v>
+      </c>
+      <c r="R183" s="5" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>555</v>
       </c>
@@ -11377,8 +14607,20 @@
         <f t="array" ref="N184">_xlfn.SWITCH(M184,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O184" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P184" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>798</v>
+      </c>
+      <c r="R184" s="5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>555</v>
       </c>
@@ -11423,8 +14665,20 @@
         <f t="array" ref="N185">_xlfn.SWITCH(M185,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O185" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P185" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>802</v>
+      </c>
+      <c r="R185" s="5" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>555</v>
       </c>
@@ -11469,8 +14723,20 @@
         <f t="array" ref="N186">_xlfn.SWITCH(M186,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O186" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P186" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>802</v>
+      </c>
+      <c r="R186" s="5" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>555</v>
       </c>
@@ -11515,8 +14781,20 @@
         <f t="array" ref="N187">_xlfn.SWITCH(M187,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O187" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P187" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>794</v>
+      </c>
+      <c r="R187" s="5" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>555</v>
       </c>
@@ -11561,8 +14839,20 @@
         <f t="array" ref="N188">_xlfn.SWITCH(M188,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O188" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P188" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>798</v>
+      </c>
+      <c r="R188" s="5" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>555</v>
       </c>
@@ -11607,8 +14897,20 @@
         <f t="array" ref="N189">_xlfn.SWITCH(M189,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O189" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P189" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>798</v>
+      </c>
+      <c r="R189" s="5" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>555</v>
       </c>
@@ -11653,8 +14955,20 @@
         <f t="array" ref="N190">_xlfn.SWITCH(M190,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O190" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P190" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>802</v>
+      </c>
+      <c r="R190" s="5" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>555</v>
       </c>
@@ -11699,8 +15013,20 @@
         <f t="array" ref="N191">_xlfn.SWITCH(M191,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O191" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P191" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>802</v>
+      </c>
+      <c r="R191" s="5" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>555</v>
       </c>
@@ -11745,8 +15071,20 @@
         <f t="array" ref="N192">_xlfn.SWITCH(M192,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O192" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P192" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>794</v>
+      </c>
+      <c r="R192" s="5" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>555</v>
       </c>
@@ -11791,8 +15129,20 @@
         <f t="array" ref="N193">_xlfn.SWITCH(M193,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O193" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P193" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>798</v>
+      </c>
+      <c r="R193" s="5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>555</v>
       </c>
@@ -11837,8 +15187,20 @@
         <f t="array" ref="N194">_xlfn.SWITCH(M194,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O194" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P194" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>798</v>
+      </c>
+      <c r="R194" s="5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>555</v>
       </c>
@@ -11883,8 +15245,20 @@
         <f t="array" ref="N195">_xlfn.SWITCH(M195,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O195" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P195" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>802</v>
+      </c>
+      <c r="R195" s="5" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>555</v>
       </c>
@@ -11929,8 +15303,20 @@
         <f t="array" ref="N196">_xlfn.SWITCH(M196,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O196" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P196" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>802</v>
+      </c>
+      <c r="R196" s="5" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>555</v>
       </c>
@@ -11975,8 +15361,20 @@
         <f t="array" ref="N197">_xlfn.SWITCH(M197,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O197" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P197" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>798</v>
+      </c>
+      <c r="R197" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>555</v>
       </c>
@@ -12021,8 +15419,20 @@
         <f t="array" ref="N198">_xlfn.SWITCH(M198,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O198" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P198" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>802</v>
+      </c>
+      <c r="R198" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>555</v>
       </c>
@@ -12067,8 +15477,20 @@
         <f t="array" ref="N199">_xlfn.SWITCH(M199,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O199" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P199" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>802</v>
+      </c>
+      <c r="R199" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>555</v>
       </c>
@@ -12113,8 +15535,20 @@
         <f t="array" ref="N200">_xlfn.SWITCH(M200,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O200" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P200" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>802</v>
+      </c>
+      <c r="R200" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>555</v>
       </c>
@@ -12159,8 +15593,20 @@
         <f t="array" ref="N201">_xlfn.SWITCH(M201,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O201" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P201" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>802</v>
+      </c>
+      <c r="R201" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>630</v>
       </c>
@@ -12205,8 +15651,20 @@
         <f t="array" ref="N202">_xlfn.SWITCH(M202,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O202" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P202" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>794</v>
+      </c>
+      <c r="R202" s="5" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>630</v>
       </c>
@@ -12251,8 +15709,20 @@
         <f t="array" ref="N203">_xlfn.SWITCH(M203,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O203" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P203" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>798</v>
+      </c>
+      <c r="R203" s="5" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>630</v>
       </c>
@@ -12297,8 +15767,20 @@
         <f t="array" ref="N204">_xlfn.SWITCH(M204,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O204" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="P204" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>798</v>
+      </c>
+      <c r="R204" s="5" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>630</v>
       </c>
@@ -12343,8 +15825,20 @@
         <f t="array" ref="N205">_xlfn.SWITCH(M205,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O205" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P205" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>802</v>
+      </c>
+      <c r="R205" s="5" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>630</v>
       </c>
@@ -12389,8 +15883,20 @@
         <f t="array" ref="N206">_xlfn.SWITCH(M206,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O206" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P206" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>802</v>
+      </c>
+      <c r="R206" s="5" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>630</v>
       </c>
@@ -12435,8 +15941,20 @@
         <f t="array" ref="N207">_xlfn.SWITCH(M207,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O207" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P207" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>798</v>
+      </c>
+      <c r="R207" s="5" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>630</v>
       </c>
@@ -12481,8 +15999,20 @@
         <f t="array" ref="N208">_xlfn.SWITCH(M208,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O208" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P208" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>802</v>
+      </c>
+      <c r="R208" s="5" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>630</v>
       </c>
@@ -12527,8 +16057,20 @@
         <f t="array" ref="N209">_xlfn.SWITCH(M209,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O209" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P209" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>802</v>
+      </c>
+      <c r="R209" s="5" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>630</v>
       </c>
@@ -12573,8 +16115,20 @@
         <f t="array" ref="N210">_xlfn.SWITCH(M210,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O210" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P210" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>802</v>
+      </c>
+      <c r="R210" s="5" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>630</v>
       </c>
@@ -12619,8 +16173,20 @@
         <f t="array" ref="N211">_xlfn.SWITCH(M211,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O211" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P211" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>802</v>
+      </c>
+      <c r="R211" s="5" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>630</v>
       </c>
@@ -12665,8 +16231,20 @@
         <f t="array" ref="N212">_xlfn.SWITCH(M212,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O212" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P212" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>794</v>
+      </c>
+      <c r="R212" s="5" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>630</v>
       </c>
@@ -12711,8 +16289,20 @@
         <f t="array" ref="N213">_xlfn.SWITCH(M213,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O213" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P213" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>798</v>
+      </c>
+      <c r="R213" s="5" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>630</v>
       </c>
@@ -12757,8 +16347,20 @@
         <f t="array" ref="N214">_xlfn.SWITCH(M214,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O214" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P214" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>798</v>
+      </c>
+      <c r="R214" s="5" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>630</v>
       </c>
@@ -12803,8 +16405,20 @@
         <f t="array" ref="N215">_xlfn.SWITCH(M215,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O215" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P215" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>802</v>
+      </c>
+      <c r="R215" s="5" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>630</v>
       </c>
@@ -12849,8 +16463,20 @@
         <f t="array" ref="N216">_xlfn.SWITCH(M216,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O216" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P216" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>802</v>
+      </c>
+      <c r="R216" s="5" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>630</v>
       </c>
@@ -12895,8 +16521,20 @@
         <f t="array" ref="N217">_xlfn.SWITCH(M217,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O217" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P217" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>798</v>
+      </c>
+      <c r="R217" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>630</v>
       </c>
@@ -12941,8 +16579,20 @@
         <f t="array" ref="N218">_xlfn.SWITCH(M218,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O218" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P218" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>802</v>
+      </c>
+      <c r="R218" s="5" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>630</v>
       </c>
@@ -12987,8 +16637,20 @@
         <f t="array" ref="N219">_xlfn.SWITCH(M219,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O219" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P219" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>802</v>
+      </c>
+      <c r="R219" s="5" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>630</v>
       </c>
@@ -13033,8 +16695,20 @@
         <f t="array" ref="N220">_xlfn.SWITCH(M220,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O220" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P220" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>802</v>
+      </c>
+      <c r="R220" s="5" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>630</v>
       </c>
@@ -13079,8 +16753,20 @@
         <f t="array" ref="N221">_xlfn.SWITCH(M221,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O221" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P221" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>802</v>
+      </c>
+      <c r="R221" s="5" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>630</v>
       </c>
@@ -13125,8 +16811,20 @@
         <f t="array" ref="N222">_xlfn.SWITCH(M222,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O222" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P222" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>794</v>
+      </c>
+      <c r="R222" s="5" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>630</v>
       </c>
@@ -13171,8 +16869,20 @@
         <f t="array" ref="N223">_xlfn.SWITCH(M223,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O223" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P223" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>798</v>
+      </c>
+      <c r="R223" s="5" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>630</v>
       </c>
@@ -13217,8 +16927,20 @@
         <f t="array" ref="N224">_xlfn.SWITCH(M224,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O224" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P224" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>798</v>
+      </c>
+      <c r="R224" s="5" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>630</v>
       </c>
@@ -13263,8 +16985,20 @@
         <f t="array" ref="N225">_xlfn.SWITCH(M225,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O225" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P225" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>802</v>
+      </c>
+      <c r="R225" s="5" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>630</v>
       </c>
@@ -13309,8 +17043,20 @@
         <f t="array" ref="N226">_xlfn.SWITCH(M226,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O226" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P226" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>802</v>
+      </c>
+      <c r="R226" s="5" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>707</v>
       </c>
@@ -13355,8 +17101,20 @@
         <f t="array" ref="N227">_xlfn.SWITCH(M227,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O227" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P227" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>790</v>
+      </c>
+      <c r="R227" s="5" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>707</v>
       </c>
@@ -13401,8 +17159,20 @@
         <f t="array" ref="N228">_xlfn.SWITCH(M228,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O228" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P228" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>794</v>
+      </c>
+      <c r="R228" s="5" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>707</v>
       </c>
@@ -13447,8 +17217,20 @@
         <f t="array" ref="N229">_xlfn.SWITCH(M229,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O229" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P229" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>798</v>
+      </c>
+      <c r="R229" s="5" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>707</v>
       </c>
@@ -13493,8 +17275,20 @@
         <f t="array" ref="N230">_xlfn.SWITCH(M230,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O230" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P230" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>802</v>
+      </c>
+      <c r="R230" s="5" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>707</v>
       </c>
@@ -13539,8 +17333,20 @@
         <f t="array" ref="N231">_xlfn.SWITCH(M231,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O231" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P231" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>802</v>
+      </c>
+      <c r="R231" s="5" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>707</v>
       </c>
@@ -13585,8 +17391,20 @@
         <f t="array" ref="N232">_xlfn.SWITCH(M232,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O232" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P232" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>790</v>
+      </c>
+      <c r="R232" s="5" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>707</v>
       </c>
@@ -13631,8 +17449,20 @@
         <f t="array" ref="N233">_xlfn.SWITCH(M233,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O233" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="P233" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>794</v>
+      </c>
+      <c r="R233" s="5" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>707</v>
       </c>
@@ -13677,8 +17507,20 @@
         <f t="array" ref="N234">_xlfn.SWITCH(M234,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O234" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P234" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>798</v>
+      </c>
+      <c r="R234" s="5" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>707</v>
       </c>
@@ -13723,8 +17565,20 @@
         <f t="array" ref="N235">_xlfn.SWITCH(M235,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O235" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P235" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>802</v>
+      </c>
+      <c r="R235" s="5" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>707</v>
       </c>
@@ -13769,8 +17623,20 @@
         <f t="array" ref="N236">_xlfn.SWITCH(M236,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O236" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P236" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>802</v>
+      </c>
+      <c r="R236" s="5" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>707</v>
       </c>
@@ -13815,8 +17681,20 @@
         <f t="array" ref="N237">_xlfn.SWITCH(M237,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O237" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P237" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>790</v>
+      </c>
+      <c r="R237" s="5" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>707</v>
       </c>
@@ -13861,8 +17739,20 @@
         <f t="array" ref="N238">_xlfn.SWITCH(M238,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Fix now</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O238" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P238" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>794</v>
+      </c>
+      <c r="R238" s="5" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>707</v>
       </c>
@@ -13907,8 +17797,20 @@
         <f t="array" ref="N239">_xlfn.SWITCH(M239,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O239" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P239" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>798</v>
+      </c>
+      <c r="R239" s="5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>707</v>
       </c>
@@ -13953,8 +17855,20 @@
         <f t="array" ref="N240">_xlfn.SWITCH(M240,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O240" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P240" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>802</v>
+      </c>
+      <c r="R240" s="5" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>707</v>
       </c>
@@ -13999,8 +17913,20 @@
         <f t="array" ref="N241">_xlfn.SWITCH(M241,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O241" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P241" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>802</v>
+      </c>
+      <c r="R241" s="5" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>707</v>
       </c>
@@ -14045,8 +17971,20 @@
         <f t="array" ref="N242">_xlfn.SWITCH(M242,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O242" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="P242" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>794</v>
+      </c>
+      <c r="R242" s="5" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>707</v>
       </c>
@@ -14091,8 +18029,20 @@
         <f t="array" ref="N243">_xlfn.SWITCH(M243,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O243" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P243" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>798</v>
+      </c>
+      <c r="R243" s="5" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>707</v>
       </c>
@@ -14137,8 +18087,20 @@
         <f t="array" ref="N244">_xlfn.SWITCH(M244,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O244" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="P244" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>798</v>
+      </c>
+      <c r="R244" s="5" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>707</v>
       </c>
@@ -14183,8 +18145,20 @@
         <f t="array" ref="N245">_xlfn.SWITCH(M245,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O245" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P245" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>802</v>
+      </c>
+      <c r="R245" s="5" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>707</v>
       </c>
@@ -14229,8 +18203,20 @@
         <f t="array" ref="N246">_xlfn.SWITCH(M246,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O246" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P246" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>802</v>
+      </c>
+      <c r="R246" s="5" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>707</v>
       </c>
@@ -14275,8 +18261,20 @@
         <f t="array" ref="N247">_xlfn.SWITCH(M247,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O247" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P247" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>794</v>
+      </c>
+      <c r="R247" s="5" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>707</v>
       </c>
@@ -14321,8 +18319,20 @@
         <f t="array" ref="N248">_xlfn.SWITCH(M248,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Plan</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O248" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P248" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>798</v>
+      </c>
+      <c r="R248" s="5" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>707</v>
       </c>
@@ -14367,8 +18377,20 @@
         <f t="array" ref="N249">_xlfn.SWITCH(M249,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O249" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P249" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>798</v>
+      </c>
+      <c r="R249" s="5" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>707</v>
       </c>
@@ -14413,8 +18435,20 @@
         <f t="array" ref="N250">_xlfn.SWITCH(M250,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O250" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P250" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>802</v>
+      </c>
+      <c r="R250" s="5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>707</v>
       </c>
@@ -14458,6 +18492,18 @@
       <c r="N251" t="str" cm="1">
         <f t="array" ref="N251">_xlfn.SWITCH(M251,12,"Fix now",11,"Fix now",10,"Fix now",9,"Fix now",8,"Plan",7,"Plan",6,"Plan",5,"Plan",4,"Accept",3,"Accept",2,"Accept",1,"Accept",0,"Accept")</f>
         <v>Accept</v>
+      </c>
+      <c r="O251" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="P251" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>802</v>
+      </c>
+      <c r="R251" s="5" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
